--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126826915</v>
+        <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>96689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2819</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råmossmyren, Råmossmyren, Dlr</t>
+          <t>Amundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437028</v>
+        <v>436955</v>
       </c>
       <c r="R2" t="n">
-        <v>6759907</v>
+        <v>6759692</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +775,74 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126826915</t>
+          <t>https://artportalen.se/Sighting/136828663</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126826931</v>
+        <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råmossmyren, Råmossmyren, Dlr</t>
+          <t>Amundbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437020</v>
+        <v>437038</v>
       </c>
       <c r="R3" t="n">
-        <v>6759912</v>
+        <v>6759848</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,18 +896,4396 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136828671</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136828674</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>437071</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6759830</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828674</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136828679</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>437112</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6759872</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828679</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136828680</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>437112</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6759842</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828680</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136828682</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>437132</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6759858</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828682</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136828684</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>437117</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6759841</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828684</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136828685</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93411</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>437119</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6759817</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828685</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126826915</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>437028</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6759907</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826915</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126826931</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Råmossmyren, Råmossmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>437020</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6759912</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126826931</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136828662</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>436903</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6759709</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828662</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136828664</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>436970</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6759736</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828664</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136828665</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>436971</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6759747</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828665</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136828666</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>436973</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6759753</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828666</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136828668</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>436977</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6759793</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828668</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136828669</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>436977</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6759802</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828669</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136828670</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>436986</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6759815</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828670</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136828672</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>437048</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6759822</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828672</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136828673</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>437038</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6759814</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828673</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136828676</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>437093</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6759852</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828676</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136828681</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>437124</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6759847</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828681</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136828683</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>437168</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6759824</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828683</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136828686</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>437115</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6759781</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828686</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136828687</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>437067</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6759753</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828687</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136828689</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>437037</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6759770</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828689</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136828690</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>437040</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6759765</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828690</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136828695</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>436935</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6759631</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828695</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136828692</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80603</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>436970</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6759707</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828692</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136828675</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>437081</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6759831</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Balgrop, äldre spillning</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828675</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136828667</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>436973</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6759774</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828667</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136828677</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>437084</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6759870</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828677</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136828678</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>437112</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6759872</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828678</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136828688</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>437068</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6759749</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828688</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136828658</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>436927</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6759660</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828658</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136828659</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>436922</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6759703</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828659</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136828660</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>436910</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6759689</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828660</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136828661</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>436898</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6759693</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828661</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136828691</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>437010</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6759698</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828691</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136828693</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>436926</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6759728</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828693</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136828694</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Amundbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>436949</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6759690</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136828694</t>
         </is>
       </c>
     </row>
@@ -906,6 +5293,44 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80603</v>
+        <v>80607</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96695</v>
+        <v>96697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80607</v>
+        <v>80609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96697</v>
+        <v>96698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96698</v>
+        <v>96704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96704</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>96710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96710</v>
+        <v>96712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96712</v>
+        <v>96725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>136828675</v>
       </c>
       <c r="B30" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96725</v>
+        <v>96727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>136828675</v>
       </c>
       <c r="B30" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136828667</v>
       </c>
       <c r="B31" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>136828677</v>
       </c>
       <c r="B32" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136828678</v>
       </c>
       <c r="B33" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>136828688</v>
       </c>
       <c r="B34" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96727</v>
+        <v>96730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96730</v>
+        <v>96740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>136828675</v>
       </c>
       <c r="B30" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>136828667</v>
       </c>
       <c r="B31" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>136828677</v>
       </c>
       <c r="B32" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>136828678</v>
       </c>
       <c r="B33" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>136828688</v>
       </c>
       <c r="B34" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96740</v>
+        <v>96741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96741</v>
+        <v>96746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>136828675</v>
       </c>
       <c r="B30" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96746</v>
+        <v>96748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96748</v>
+        <v>96754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37535-2026 artfynd.xlsx
+++ b/artfynd/A 37535-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136828663</v>
       </c>
       <c r="B2" t="n">
-        <v>96754</v>
+        <v>96766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136828671</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>136828674</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         <v>136828679</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>136828680</v>
       </c>
       <c r="B6" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>136828682</v>
       </c>
       <c r="B7" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>136828684</v>
       </c>
       <c r="B8" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>136828685</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>136828662</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136828664</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>136828665</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>136828666</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>136828668</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136828669</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>136828670</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,7 +2650,7 @@
         <v>136828672</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136828673</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>136828676</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136828681</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>136828683</v>
       </c>
       <c r="B23" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>136828686</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3322,7 @@
         <v>136828687</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>136828689</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>136828690</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>136828695</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>136828692</v>
       </c>
       <c r="B29" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>136828658</v>
       </c>
       <c r="B35" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136828659</v>
       </c>
       <c r="B36" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>136828660</v>
       </c>
       <c r="B37" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>136828661</v>
       </c>
       <c r="B38" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>136828691</v>
       </c>
       <c r="B39" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>136828693</v>
       </c>
       <c r="B40" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>136828694</v>
       </c>
       <c r="B41" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
